--- a/docs/downloads/11/tbl_cultures_touchees_alaotra_ambohidrony.xlsx
+++ b/docs/downloads/11/tbl_cultures_touchees_alaotra_ambohidrony.xlsx
@@ -603,12 +603,6 @@
           <t>Brède</t>
         </is>
       </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14">
-        <v>6.2</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -621,12 +615,6 @@
           <t>mais</t>
         </is>
       </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15">
-        <v>6.2</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -639,12 +627,6 @@
           <t>Courge</t>
         </is>
       </c>
-      <c r="C16">
-        <v>3</v>
-      </c>
-      <c r="D16">
-        <v>4.7</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -657,12 +639,6 @@
           <t>Courgette</t>
         </is>
       </c>
-      <c r="C17">
-        <v>3</v>
-      </c>
-      <c r="D17">
-        <v>4.7</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -675,12 +651,6 @@
           <t>Mangue</t>
         </is>
       </c>
-      <c r="C18">
-        <v>3</v>
-      </c>
-      <c r="D18">
-        <v>4.7</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -693,12 +663,6 @@
           <t>manioc</t>
         </is>
       </c>
-      <c r="C19">
-        <v>3</v>
-      </c>
-      <c r="D19">
-        <v>4.7</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -711,12 +675,6 @@
           <t>Orange</t>
         </is>
       </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20">
-        <v>3.1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -728,12 +686,6 @@
         <is>
           <t>tamarin</t>
         </is>
-      </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21">
-        <v>3.1</v>
       </c>
     </row>
   </sheetData>
